--- a/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-051, 25-075, 24-041, 24-045, 24-052</t>
+          <t>25-084, 25-085, 23-099, 24-010, 23-021</t>
         </is>
       </c>
     </row>
@@ -635,17 +628,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +713,8 @@
       <c r="E9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>5.5</v>
+      <c r="F9" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2.0-9.0</t>
+          <t>ratio=1.00 (0.75-1.33)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +750,8 @@
       <c r="E10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>9</v>
+      <c r="F10" s="9" t="n">
+        <v>11.2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>5.0-12.0</t>
+          <t>ratio=1.25 (0.86-1.55)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,8 +787,8 @@
       <c r="E11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>3</v>
+      <c r="F11" s="10" t="n">
+        <v>2.8</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -806,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.56 (n=1)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,7 +824,7 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -843,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -870,7 +861,7 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -880,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -907,8 +898,8 @@
       <c r="E14" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>2</v>
+      <c r="F14" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -917,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -944,8 +935,8 @@
       <c r="E15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>4.8</v>
+      <c r="F15" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -954,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=1.00 (1.00-1.75)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -981,8 +972,8 @@
       <c r="E16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>4.5</v>
+      <c r="F16" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -991,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>4.0-21.0</t>
+          <t>ratio=1.00 (0.75-1.12)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1035,7 +1026,7 @@
       <c r="E18" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -1045,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>7.0-18.5</t>
+          <t>ratio=1.10 (0.73-1.46)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1072,8 +1063,8 @@
       <c r="E19" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>9</v>
+      <c r="F19" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1082,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>1.0-22.0</t>
+          <t>ratio=0.50 (0.47-1.00)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1126,7 +1117,7 @@
       <c r="E21" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1136,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>2.0-21.5</t>
+          <t>ratio=1.00 (0.75-1.50)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1180,8 +1171,8 @@
       <c r="E23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>2</v>
+      <c r="F23" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1190,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>1.5-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1217,17 +1208,17 @@
       <c r="E24" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.33)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1272,12 +1263,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,8 +1295,8 @@
       <c r="E27" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>10</v>
+      <c r="F27" s="9" t="n">
+        <v>4.7</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>4.0-13.5</t>
+          <t>ratio=0.94 (0.63-1.38)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1341,8 +1332,8 @@
       <c r="E28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>11</v>
+      <c r="F28" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1351,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>7.0-12.0</t>
+          <t>ratio=0.90 (0.61-1.50)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1395,17 +1386,17 @@
       <c r="E30" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>7.0-14.0</t>
+          <t>ratio=0.88 (0.75-1.08)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1430,17 +1421,15 @@
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
-      <c r="F31" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,8 +1456,8 @@
       <c r="E32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>3.8</v>
+      <c r="F32" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>1.5-7.5</t>
+          <t>ratio=1.50 (0.30-2.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,8 +1493,8 @@
       <c r="E33" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>2</v>
+      <c r="F33" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>1.5-29.0</t>
+          <t>ratio=1.00 (0.62-1.38)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1541,8 +1530,8 @@
       <c r="E34" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>4</v>
+      <c r="F34" s="9" t="n">
+        <v>6.3</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1551,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>2.5-10.5</t>
+          <t>ratio=0.79 (0.39-1.00)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1578,8 +1567,8 @@
       <c r="E35" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>5.2</v>
+      <c r="F35" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1588,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2.5-8.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1632,8 +1621,8 @@
       <c r="E37" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>15</v>
+      <c r="F37" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1642,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>1.0-26.0</t>
+          <t>ratio=0.90 (0.50-1.86)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1686,8 +1675,8 @@
       <c r="E39" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>9</v>
+      <c r="F39" s="9" t="n">
+        <v>13.2</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1696,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>5.0-14.0</t>
+          <t>ratio=1.10 (0.59-1.86)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1723,8 +1712,8 @@
       <c r="E40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>15</v>
+      <c r="F40" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1733,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>3.0-23.0</t>
+          <t>ratio=1.10 (1.00-1.33)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1760,8 +1749,8 @@
       <c r="E41" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>12</v>
+      <c r="F41" s="9" t="n">
+        <v>6.4</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1770,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>12.0-25.0</t>
+          <t>ratio=2.15 (1.17-4.00)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1797,8 +1786,8 @@
       <c r="E42" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>5</v>
+      <c r="F42" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1807,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>2.5-5.0</t>
+          <t>ratio=1.20 (0.67-2.20)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1834,8 +1823,8 @@
       <c r="E43" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>5.5</v>
+      <c r="F43" s="9" t="n">
+        <v>6.4</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1844,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>4.0-5.5</t>
+          <t>ratio=1.07 (0.92-1.80)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1872,16 +1861,16 @@
         <v>4</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.62 (n=2)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1906,17 +1895,15 @@
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
-      <c r="F45" s="11" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1943,8 +1930,8 @@
       <c r="E46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>6.8</v>
+      <c r="F46" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1953,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>5.5-13.5</t>
+          <t>ratio=1.00 (0.78-2.12)</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1980,8 +1967,8 @@
       <c r="E47" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>15.5</v>
+      <c r="F47" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1990,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>15.0-42.5</t>
+          <t>ratio=1.00 (0.80-1.29)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2017,8 +2004,8 @@
       <c r="E48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>6</v>
+      <c r="F48" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2027,7 +2014,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>3.0-6.5</t>
+          <t>ratio=1.00 (0.20-2.50)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2071,8 +2058,8 @@
       <c r="E50" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>2</v>
+      <c r="F50" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2081,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=0.69 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2108,8 +2095,8 @@
       <c r="E51" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>8</v>
+      <c r="F51" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2118,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>2.0-12.0</t>
+          <t>ratio=0.80 (0.67-1.00)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2145,8 +2132,8 @@
       <c r="E52" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>9.5</v>
+      <c r="F52" s="9" t="n">
+        <v>18.8</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2155,7 +2142,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>3.0-24.5</t>
+          <t>ratio=0.75 (0.36-1.07)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2182,7 +2169,7 @@
       <c r="E53" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="10" t="n">
+      <c r="F53" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -2192,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.00 (0.25-1.00)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2236,17 +2223,17 @@
       <c r="E55" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="11" t="n">
-        <v>4</v>
+      <c r="F55" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>4.0-4.0</t>
+          <t>ratio=1.25 (1.00-3.50)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2271,17 +2258,15 @@
         </is>
       </c>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2325,8 +2310,8 @@
       <c r="E58" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="10" t="n">
-        <v>2.2</v>
+      <c r="F58" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2335,7 +2320,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.5</t>
+          <t>ratio=3.62 (1.25-5.00)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2362,8 +2347,8 @@
       <c r="E59" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>15</v>
+      <c r="F59" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2372,7 +2357,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>6.0-15.8</t>
+          <t>ratio=0.58 (0.33-2.11)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2400,12 +2385,12 @@
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2433,12 +2418,12 @@
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2465,8 +2450,8 @@
       <c r="E62" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="11" t="n">
-        <v>2</v>
+      <c r="F62" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2475,7 +2460,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=4.00 (n=1)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2503,12 +2488,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2536,12 +2521,12 @@
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2585,8 +2570,8 @@
       <c r="E66" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="10" t="n">
-        <v>4</v>
+      <c r="F66" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2595,7 +2580,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>2.0-20.5</t>
+          <t>ratio=3.25 (2.25-4.25)</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2623,12 +2608,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2655,8 +2640,8 @@
       <c r="E68" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F68" s="10" t="n">
-        <v>6</v>
+      <c r="F68" s="9" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2665,7 +2650,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>2.0-14.5</t>
+          <t>ratio=2.20 (0.83-4.25)</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2679,7 +2664,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>264.3</v>
+        <v>238.7</v>
       </c>
     </row>
   </sheetData>
@@ -2747,7 +2732,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-051, 25-075, 24-041, 24-045, 24-052</t>
+          <t>25-084, 25-085, 23-099, 24-010, 23-021</t>
         </is>
       </c>
     </row>
@@ -4411,35 +4396,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-051</t>
+          <t>25-084</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-075</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-041</t>
+          <t>23-099</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-045</t>
+          <t>24-010</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-052</t>
+          <t>23-021</t>
         </is>
       </c>
     </row>
@@ -4494,23 +4479,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4528,19 +4509,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24-041, 24-045, 24-051, 24-052, 25-075</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4554,7 +4531,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4563,12 +4540,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.0-9.0</t>
+          <t>ratio=1.00 (0.75-1.33)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4561,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4593,12 +4570,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.0-12.0</t>
+          <t>ratio=1.25 (0.86-1.55)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4591,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4623,12 +4600,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.56 (n=1)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-075, 24-052</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
@@ -4653,12 +4630,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4683,12 +4660,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24-052, 24-051, 24-045</t>
+          <t>25-085, 25-084, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4681,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4713,12 +4690,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4711,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4743,12 +4720,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=1.00 (1.00-1.75)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4741,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4773,12 +4750,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.0-21.0</t>
+          <t>ratio=1.00 (0.75-1.12)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4780,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.0-18.5</t>
+          <t>ratio=1.10 (0.73-1.46)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4801,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4833,12 +4810,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.0-22.0</t>
+          <t>ratio=0.50 (0.47-1.00)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4840,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-21.5</t>
+          <t>ratio=1.00 (0.75-1.50)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4861,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4893,12 +4870,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4918,17 +4895,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.33)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-075, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -4948,19 +4925,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>24-041, 24-045, 24-051, 24-052, 25-075</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4974,7 +4947,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4983,12 +4956,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.0-13.5</t>
+          <t>ratio=0.94 (0.63-1.38)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5004,7 +4977,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5013,12 +4986,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.0-12.0</t>
+          <t>ratio=0.90 (0.61-1.50)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5038,17 +5011,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.0-14.0</t>
+          <t>ratio=0.88 (0.75-1.08)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5064,23 +5037,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5094,7 +5063,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5103,12 +5072,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5-7.5</t>
+          <t>ratio=1.50 (0.30-2.00)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-075, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5093,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5133,12 +5102,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5-29.0</t>
+          <t>ratio=1.00 (0.62-1.38)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5123,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5163,12 +5132,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.5-10.5</t>
+          <t>ratio=0.79 (0.39-1.00)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5153,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5193,12 +5162,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.5-8.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-075, 24-052</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5183,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5223,12 +5192,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0-26.0</t>
+          <t>ratio=0.90 (0.50-1.86)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-075, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5244,23 +5213,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5274,7 +5239,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>13.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5283,12 +5248,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.0-14.0</t>
+          <t>ratio=1.10 (0.59-1.86)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5269,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5313,12 +5278,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.0-23.0</t>
+          <t>ratio=1.10 (1.00-1.33)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051</t>
+          <t>25-085, 25-084, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5299,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5343,12 +5308,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12.0-25.0</t>
+          <t>ratio=2.15 (1.17-4.00)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051</t>
+          <t>25-085, 25-084, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5329,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5373,12 +5338,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.5-5.0</t>
+          <t>ratio=1.20 (0.67-2.20)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5359,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5403,12 +5368,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.0-5.5</t>
+          <t>ratio=1.07 (0.92-1.80)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5424,21 +5389,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.62 (n=2)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-084, 23-021</t>
         </is>
       </c>
     </row>
@@ -5454,23 +5419,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5-1.5</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5484,7 +5445,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5493,12 +5454,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5.5-13.5</t>
+          <t>ratio=1.00 (0.78-2.12)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5475,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5523,12 +5484,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15.0-42.5</t>
+          <t>ratio=1.00 (0.80-1.29)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-041</t>
+          <t>25-085, 25-084, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5505,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5553,12 +5514,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3.0-6.5</t>
+          <t>ratio=1.00 (0.20-2.50)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5535,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5583,12 +5544,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=0.69 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5565,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5613,12 +5574,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.0-12.0</t>
+          <t>ratio=0.80 (0.67-1.00)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5595,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9.5</v>
+        <v>18.8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5643,12 +5604,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3.0-24.5</t>
+          <t>ratio=0.75 (0.36-1.07)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5634,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.00 (0.25-1.00)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5694,21 +5655,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4.0-4.0</t>
+          <t>ratio=1.25 (1.00-3.50)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5724,23 +5685,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5754,7 +5711,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5763,12 +5720,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.0-4.5</t>
+          <t>ratio=3.62 (1.25-5.00)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5741,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5793,12 +5750,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6.0-15.8</t>
+          <t>ratio=0.58 (0.33-2.11)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5818,19 +5775,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>24-041, 24-045, 24-051, 24-052, 25-075</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5848,19 +5801,15 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>24-041</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5874,7 +5823,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5883,12 +5832,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=4.00 (n=1)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-041</t>
+          <t>25-084</t>
         </is>
       </c>
     </row>
@@ -5908,19 +5857,15 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>24-041, 24-051, 24-052, 25-075</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5938,19 +5883,15 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>24-041, 24-051, 24-052, 25-075</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5964,7 +5905,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5973,12 +5914,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2.0-20.5</t>
+          <t>ratio=3.25 (2.25-4.25)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>
@@ -5998,19 +5939,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>24-041, 24-045, 24-051, 24-052, 25-075</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6024,7 +5961,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6033,12 +5970,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.0-14.5</t>
+          <t>ratio=2.20 (0.83-4.25)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-075, 24-052, 24-051, 24-045, 24-041</t>
+          <t>25-085, 24-010, 23-099, 23-021</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-084, 25-085, 23-099, 24-010, 23-021</t>
+          <t>25-084, 25-085, 23-021, 24-010, 23-099</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-084, 25-085, 23-099, 24-010, 23-021</t>
+          <t>25-084, 25-085, 23-021, 24-010, 23-099</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-099</t>
+          <t>23-021</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-021</t>
+          <t>23-099</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-084, 25-085, 23-021, 24-010, 23-099</t>
+          <t>25-084, 23-094, 23-099, 23-095, 23-098</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -664,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.33)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>11.2</v>
+        <v>13.3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.86-1.55)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -787,17 +787,17 @@
       <c r="E11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>2.8</v>
+      <c r="F11" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.56 (n=1)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -825,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -899,7 +899,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -936,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.75)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -973,7 +973,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.12)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1027,7 +1027,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>16.5</v>
+        <v>20.6</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.73-1.46)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.47-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.50)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1209,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.33)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1263,12 +1263,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.63-1.38)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.61-1.50)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1387,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.08)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1424,12 +1424,12 @@
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.30-2.00)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.38)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>6.3</v>
+        <v>11.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.39-1.00)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1567,17 +1567,17 @@
       <c r="E35" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>7</v>
+      <c r="F35" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.50-1.86)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.59-1.86)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1713,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (1.00-1.33)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.15 (1.17-4.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1787,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.67-2.20)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.07 (0.92-1.80)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1860,17 +1860,17 @@
       <c r="E44" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>2.5</v>
+      <c r="F44" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (n=2)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1898,12 +1898,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.78-2.12)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>4</v>
+        <v>17.6</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-1.29)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2004,17 +2004,17 @@
       <c r="E48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="10" t="n">
         <v>2</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.20-2.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2059,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.50-1.50)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2096,7 +2096,7 @@
         <v>6</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.67-1.00)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2133,7 +2133,7 @@
         <v>25</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>18.8</v>
+        <v>21.1</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.36-1.07)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2170,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-1.00)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2224,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-3.50)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2261,12 +2261,12 @@
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2311,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.62 (1.25-5.00)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2348,7 +2348,7 @@
         <v>12</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>7</v>
+        <v>22.5</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.33-2.11)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2385,12 +2385,12 @@
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2418,12 +2418,12 @@
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2450,17 +2450,17 @@
       <c r="E62" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="10" t="n">
-        <v>8</v>
+      <c r="F62" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=4.00 (n=1)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2488,12 +2488,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2521,12 +2521,12 @@
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2571,7 +2571,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.25 (2.25-4.25)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2608,12 +2608,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.20 (0.83-4.25)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>238.7</v>
+        <v>269.4</v>
       </c>
     </row>
   </sheetData>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-084, 25-085, 23-021, 24-010, 23-099</t>
+          <t>25-084, 23-094, 23-099, 23-095, 23-098</t>
         </is>
       </c>
     </row>
@@ -4403,28 +4403,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-085</t>
+          <t>23-094</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-021</t>
+          <t>23-099</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-010</t>
+          <t>23-095</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-099</t>
+          <t>23-098</t>
         </is>
       </c>
     </row>
@@ -4483,15 +4483,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4509,15 +4513,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4531,7 +4539,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4540,12 +4548,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.33)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4569,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.2</v>
+        <v>13.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4570,12 +4578,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.86-1.55)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4591,21 +4599,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.56 (n=1)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-085</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4629,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4630,12 +4638,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4659,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4660,12 +4668,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4689,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4690,12 +4698,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4719,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4720,12 +4728,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.75)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4749,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4750,12 +4758,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.12)</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4779,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.5</v>
+        <v>20.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4780,12 +4788,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.73-1.46)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4809,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4810,12 +4818,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.47-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4839,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4840,12 +4848,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.50)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4870,12 +4878,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4899,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4900,12 +4908,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.33)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4925,15 +4933,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4947,7 +4959,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4956,12 +4968,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.63-1.38)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4989,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4986,12 +4998,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.61-1.50)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 23-099, 23-021</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5019,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5016,12 +5028,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.08)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5041,15 +5053,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5063,7 +5079,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5072,12 +5088,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.30-2.00)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5109,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5102,12 +5118,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.38)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5139,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.3</v>
+        <v>11.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5132,12 +5148,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.39-1.00)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5153,21 +5169,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:32h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-085</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5199,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5192,12 +5208,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.50-1.86)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5217,15 +5233,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5239,7 +5259,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5248,12 +5268,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.10 (0.59-1.86)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5289,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,12 +5298,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.10 (1.00-1.33)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5319,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5308,12 +5328,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=2.15 (1.17-4.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5349,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,12 +5358,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.67-2.20)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5379,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5368,12 +5388,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.07 (0.92-1.80)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5389,21 +5409,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=0.62 (n=2)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-084, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5423,15 +5443,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5445,7 +5469,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,12 +5478,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.78-2.12)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5499,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>17.6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,12 +5508,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-1.29)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 23-099, 23-021</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5509,17 +5533,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.20-2.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5559,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5544,12 +5568,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.50-1.50)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5589,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5574,12 +5598,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.67-1.00)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5619,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18.8</v>
+        <v>21.1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5604,12 +5628,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.36-1.07)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5649,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5634,12 +5658,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-1.00)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5679,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5664,12 +5688,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-3.50)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-084, 24-010, 23-099, 23-021</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5689,15 +5713,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5711,7 +5739,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5720,12 +5748,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=3.62 (1.25-5.00)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24-010, 23-099, 23-021</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5769,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>22.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5750,12 +5778,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.33-2.11)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-085, 25-084, 24-010, 23-099, 23-021</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5775,15 +5803,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5801,15 +5833,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5823,21 +5859,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=4.00 (n=1)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-084</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5857,15 +5893,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5883,15 +5923,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5905,7 +5949,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5914,12 +5958,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=3.25 (2.25-4.25)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5939,15 +5983,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5961,7 +6009,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5970,12 +6018,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ratio=2.20 (0.83-4.25)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>25-085, 24-010, 23-099, 23-021</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-080 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -973,7 +973,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1027,7 +1027,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1209,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1387,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1713,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1787,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1861,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1968,7 +1968,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2059,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2096,7 +2096,7 @@
         <v>6</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>10.6</v>
+        <v>8.1</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2133,7 +2133,7 @@
         <v>25</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>21.1</v>
+        <v>16.1</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2170,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2224,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2311,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2348,7 +2348,7 @@
         <v>12</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2451,7 +2451,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2571,7 +2571,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>269.4</v>
+        <v>247.1</v>
       </c>
     </row>
   </sheetData>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:31h</t>
+          <t>group_total:30h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:32h</t>
+          <t>group_total:31h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10.6</v>
+        <v>8.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>21.1</v>
+        <v>16.1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:29h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:41h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
